--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260914.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260914.xlsx
@@ -623,17 +623,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>34,687,185</t>
+          <t>724,260,685</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -645,17 +645,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>724,260,685</t>
+          <t>34,687,185</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
